--- a/dados_locacao.xlsx
+++ b/dados_locacao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Downloads\Python\Dashboard_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E4C8E8-D614-43A0-8BD2-5BD1BF43C26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227A1AA9-C0C6-4317-B000-A9873369053F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6BD35C78-8BAC-46C2-ABDD-68B806E82333}"/>
   </bookViews>
@@ -187,10 +187,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+  <numFmts count="3">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,6 +225,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -250,7 +259,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -333,11 +342,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -354,17 +380,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -381,8 +401,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
+    <cellStyle name="Moeda 2" xfId="2" xr:uid="{73C2B2FB-DE5F-4E90-8642-8C3DF62AE737}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -739,31 +777,31 @@
       <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="6">
-        <v>3200</v>
-      </c>
-      <c r="F2" s="6">
-        <v>3800</v>
+      <c r="E2" s="14">
+        <v>2116</v>
+      </c>
+      <c r="F2" s="14">
+        <v>2433.4</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="9">
-        <v>1600</v>
-      </c>
-      <c r="F3" s="9">
-        <v>2400</v>
+      <c r="E3" s="14">
+        <v>1840</v>
+      </c>
+      <c r="F3" s="14">
+        <v>2116</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -779,28 +817,32 @@
       <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="6">
-        <v>280</v>
-      </c>
-      <c r="F4" s="6">
-        <v>320</v>
+      <c r="E4" s="14">
+        <v>234.6</v>
+      </c>
+      <c r="F4" s="14">
+        <v>269.78999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="E5" s="14">
+        <v>2484</v>
+      </c>
+      <c r="F5" s="14">
+        <v>2856.6</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
@@ -809,30 +851,38 @@
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="E6" s="14">
+        <v>2070</v>
+      </c>
+      <c r="F6" s="14">
+        <v>2380.5</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="E7" s="14">
+        <v>248.4</v>
+      </c>
+      <c r="F7" s="14">
+        <v>285.66000000000003</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
@@ -847,24 +897,32 @@
       <c r="D8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="E8" s="13">
+        <v>2760</v>
+      </c>
+      <c r="F8" s="13">
+        <v>3174</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="C9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="E9" s="13">
+        <v>2300</v>
+      </c>
+      <c r="F9" s="13">
+        <v>2645</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
@@ -879,24 +937,32 @@
       <c r="D10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="E10" s="13">
+        <v>271.39999999999998</v>
+      </c>
+      <c r="F10" s="13">
+        <v>312.10999999999996</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="13">
+        <v>3036</v>
+      </c>
+      <c r="F11" s="13">
+        <v>3491.4</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
@@ -905,30 +971,38 @@
       <c r="B12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="E12" s="13">
+        <v>2484</v>
+      </c>
+      <c r="F12" s="13">
+        <v>2856.6</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="13">
+        <v>299</v>
+      </c>
+      <c r="F13" s="13">
+        <v>343.85</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
@@ -943,24 +1017,32 @@
       <c r="D14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="E14" s="16">
+        <v>3312</v>
+      </c>
+      <c r="F14" s="16">
+        <v>3808.8</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="C15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="E15" s="17">
+        <v>2530</v>
+      </c>
+      <c r="F15" s="17">
+        <v>2909.5</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
@@ -975,24 +1057,32 @@
       <c r="D16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="E16" s="16">
+        <v>322</v>
+      </c>
+      <c r="F16" s="16">
+        <v>370.3</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="E17" s="16">
+        <v>4118.3999999999996</v>
+      </c>
+      <c r="F17" s="16">
+        <v>4736.16</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
@@ -1001,30 +1091,38 @@
       <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="E18" s="17">
+        <v>2880</v>
+      </c>
+      <c r="F18" s="17">
+        <v>3312</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="E19" s="16">
+        <v>408</v>
+      </c>
+      <c r="F19" s="16">
+        <v>469.2</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
@@ -1039,24 +1137,32 @@
       <c r="D20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="E20" s="17">
+        <v>4320</v>
+      </c>
+      <c r="F20" s="17">
+        <v>4968</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="C21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="E21" s="16">
+        <v>3180</v>
+      </c>
+      <c r="F21" s="16">
+        <v>3657</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
@@ -1071,24 +1177,32 @@
       <c r="D22" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="E22" s="17">
+        <v>432</v>
+      </c>
+      <c r="F22" s="17">
+        <v>496.8</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="E23" s="16">
+        <v>5184</v>
+      </c>
+      <c r="F23" s="16">
+        <v>5961.6</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
@@ -1097,30 +1211,38 @@
       <c r="B24" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="E24" s="17">
+        <v>3600</v>
+      </c>
+      <c r="F24" s="17">
+        <v>4140</v>
+      </c>
     </row>
     <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
+      <c r="E25" s="16">
+        <v>456</v>
+      </c>
+      <c r="F25" s="16">
+        <v>524.4</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
@@ -1135,24 +1257,32 @@
       <c r="D26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
+      <c r="E26" s="17">
+        <v>7800</v>
+      </c>
+      <c r="F26" s="17">
+        <v>9000</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="8" t="s">
+      <c r="C27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
+      <c r="E27" s="16">
+        <v>5800</v>
+      </c>
+      <c r="F27" s="16">
+        <v>6400</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
@@ -1167,24 +1297,32 @@
       <c r="D28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="E28" s="17">
+        <v>700</v>
+      </c>
+      <c r="F28" s="17">
+        <v>900</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
+      <c r="E29" s="16">
+        <v>9500</v>
+      </c>
+      <c r="F29" s="16">
+        <v>10800</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
@@ -1193,30 +1331,38 @@
       <c r="B30" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
+      <c r="E30" s="17">
+        <v>5900</v>
+      </c>
+      <c r="F30" s="17">
+        <v>6400</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
+      <c r="E31" s="16">
+        <v>864</v>
+      </c>
+      <c r="F31" s="16">
+        <v>993.6</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
@@ -1231,24 +1377,32 @@
       <c r="D32" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="E32" s="13">
+        <v>9500</v>
+      </c>
+      <c r="F32" s="13">
+        <v>10800</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="8" t="s">
+      <c r="C33" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
+      <c r="E33" s="13">
+        <v>5796</v>
+      </c>
+      <c r="F33" s="13">
+        <v>6665.4</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
@@ -1263,24 +1417,32 @@
       <c r="D34" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="E34" s="13">
+        <v>900</v>
+      </c>
+      <c r="F34" s="13">
+        <v>1200</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
+      <c r="E35" s="16">
+        <v>11000</v>
+      </c>
+      <c r="F35" s="18">
+        <v>12500</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
@@ -1289,30 +1451,38 @@
       <c r="B36" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="E36" s="17">
+        <v>7500</v>
+      </c>
+      <c r="F36" s="18">
+        <v>9000</v>
+      </c>
     </row>
     <row r="37" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
+      <c r="E37" s="16">
+        <v>948.75</v>
+      </c>
+      <c r="F37" s="18">
+        <v>1091.0625</v>
+      </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
@@ -1327,10 +1497,10 @@
       <c r="D38" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="19">
         <v>10200</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="19">
         <v>16800</v>
       </c>
     </row>
@@ -1338,19 +1508,19 @@
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="8" t="s">
+      <c r="C39" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="20">
         <v>7300</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="20">
         <v>8000</v>
       </c>
     </row>
@@ -1367,10 +1537,10 @@
       <c r="D40" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="19">
         <v>1200</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40" s="19">
         <v>1600</v>
       </c>
     </row>
@@ -1384,27 +1554,35 @@
       <c r="C41" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="10"/>
+      <c r="E41" s="15">
+        <v>7200</v>
+      </c>
+      <c r="F41" s="15">
+        <v>7200</v>
+      </c>
     </row>
     <row r="42" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="14" t="s">
+      <c r="C42" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="10"/>
+      <c r="E42" s="15">
+        <v>4800</v>
+      </c>
+      <c r="F42" s="15">
+        <v>4800</v>
+      </c>
     </row>
     <row r="43" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
@@ -1416,17 +1594,21 @@
       <c r="C43" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="10"/>
+      <c r="E43" s="15">
+        <v>600</v>
+      </c>
+      <c r="F43" s="15">
+        <v>600</v>
+      </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C44" s="5" t="s">
@@ -1435,30 +1617,38 @@
       <c r="D44" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="10"/>
+      <c r="E44" s="15">
+        <v>12700</v>
+      </c>
+      <c r="F44" s="15">
+        <v>12700</v>
+      </c>
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="10"/>
+      <c r="E45" s="15">
+        <v>7400</v>
+      </c>
+      <c r="F45" s="15">
+        <v>7400</v>
+      </c>
     </row>
     <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C46" s="5" t="s">
@@ -1467,8 +1657,12 @@
       <c r="D46" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="10"/>
+      <c r="E46" s="15">
+        <v>1800</v>
+      </c>
+      <c r="F46" s="15">
+        <v>1800</v>
+      </c>
     </row>
     <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
@@ -1483,24 +1677,32 @@
       <c r="D47" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="10"/>
+      <c r="E47" s="15">
+        <v>17500</v>
+      </c>
+      <c r="F47" s="15">
+        <v>17500</v>
+      </c>
     </row>
     <row r="48" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="8" t="s">
+      <c r="C48" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="10"/>
+      <c r="E48" s="15">
+        <v>10400</v>
+      </c>
+      <c r="F48" s="15">
+        <v>10400</v>
+      </c>
     </row>
     <row r="49" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
@@ -1515,24 +1717,28 @@
       <c r="D49" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="10"/>
+      <c r="E49" s="15">
+        <v>2000</v>
+      </c>
+      <c r="F49" s="15">
+        <v>2000</v>
+      </c>
     </row>
     <row r="50" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="10"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="8"/>
     </row>
     <row r="51" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
@@ -1541,30 +1747,30 @@
       <c r="B51" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="14" t="s">
+      <c r="C51" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>49</v>
       </c>
       <c r="E51" s="5"/>
-      <c r="F51" s="10"/>
+      <c r="F51" s="8"/>
     </row>
     <row r="52" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E52" s="8"/>
-      <c r="F52" s="10"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="8"/>
     </row>
     <row r="53" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
@@ -1576,27 +1782,27 @@
       <c r="C53" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="12" t="s">
         <v>47</v>
       </c>
       <c r="E53" s="5"/>
-      <c r="F53" s="10"/>
+      <c r="F53" s="8"/>
     </row>
     <row r="54" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54" s="14" t="s">
+      <c r="C54" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E54" s="8"/>
-      <c r="F54" s="10"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="8"/>
     </row>
     <row r="55" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
@@ -1608,11 +1814,11 @@
       <c r="C55" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="12" t="s">
         <v>47</v>
       </c>
       <c r="E55" s="5"/>
-      <c r="F55" s="13"/>
+      <c r="F55" s="11"/>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
@@ -1628,23 +1834,23 @@
         <v>35</v>
       </c>
       <c r="E56" s="5"/>
-      <c r="F56" s="13"/>
+      <c r="F56" s="11"/>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C57" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" s="8" t="s">
+      <c r="C57" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E57" s="8"/>
-      <c r="F57" s="13"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="11"/>
     </row>
     <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
@@ -1660,55 +1866,55 @@
         <v>35</v>
       </c>
       <c r="E58" s="5"/>
-      <c r="F58" s="13"/>
+      <c r="F58" s="11"/>
     </row>
     <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E59" s="8"/>
-      <c r="F59" s="13"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="11"/>
     </row>
     <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E60" s="5"/>
-      <c r="F60" s="13"/>
+      <c r="F60" s="11"/>
     </row>
     <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="13"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="11"/>
     </row>
     <row r="62" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
@@ -1721,20 +1927,20 @@
         <v>5</v>
       </c>
       <c r="E62" s="5"/>
-      <c r="F62" s="13"/>
+      <c r="F62" s="11"/>
     </row>
     <row r="63" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" s="8"/>
-      <c r="F63" s="13"/>
+      <c r="C63" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" s="7"/>
+      <c r="F63" s="11"/>
     </row>
     <row r="64" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
@@ -1747,19 +1953,19 @@
         <v>8</v>
       </c>
       <c r="E64" s="5"/>
-      <c r="F64" s="13"/>
+      <c r="F64" s="11"/>
     </row>
     <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="13"/>
+      <c r="F65" s="11"/>
     </row>
     <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
@@ -1768,22 +1974,22 @@
       <c r="B66" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C66" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" s="13"/>
+      <c r="C66" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F66" s="11"/>
     </row>
     <row r="67" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F67" s="13"/>
+      <c r="F67" s="11"/>
     </row>
     <row r="68" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
@@ -1799,23 +2005,23 @@
         <v>16</v>
       </c>
       <c r="E68" s="5"/>
-      <c r="F68" s="13"/>
+      <c r="F68" s="11"/>
     </row>
     <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C69" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69" s="8" t="s">
+      <c r="C69" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E69" s="8"/>
-      <c r="F69" s="13"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="11"/>
     </row>
     <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
@@ -1831,7 +2037,7 @@
         <v>16</v>
       </c>
       <c r="E70" s="5"/>
-      <c r="F70" s="13"/>
+      <c r="F70" s="11"/>
     </row>
     <row r="71" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="1" t="s">
@@ -1847,23 +2053,23 @@
         <v>35</v>
       </c>
       <c r="E71" s="5"/>
-      <c r="F71" s="13"/>
+      <c r="F71" s="11"/>
     </row>
     <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C72" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D72" s="8" t="s">
+      <c r="C72" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E72" s="8"/>
-      <c r="F72" s="13"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="11"/>
     </row>
     <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
@@ -1879,55 +2085,55 @@
         <v>35</v>
       </c>
       <c r="E73" s="5"/>
-      <c r="F73" s="13"/>
+      <c r="F73" s="11"/>
     </row>
     <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D74" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E74" s="8"/>
-      <c r="F74" s="13"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="11"/>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E75" s="5"/>
-      <c r="F75" s="13"/>
+      <c r="F75" s="11"/>
     </row>
     <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="8" t="s">
+      <c r="D76" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E76" s="8"/>
-      <c r="F76" s="13"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="11"/>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="1" t="s">
@@ -1943,23 +2149,23 @@
         <v>12</v>
       </c>
       <c r="E77" s="5"/>
-      <c r="F77" s="13"/>
+      <c r="F77" s="11"/>
     </row>
     <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C78" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D78" s="8" t="s">
+      <c r="C78" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E78" s="8"/>
-      <c r="F78" s="13"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="11"/>
     </row>
     <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="1" t="s">
@@ -1975,23 +2181,23 @@
         <v>12</v>
       </c>
       <c r="E79" s="5"/>
-      <c r="F79" s="13"/>
+      <c r="F79" s="11"/>
     </row>
     <row r="80" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D80" s="8" t="s">
+      <c r="D80" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E80" s="8"/>
-      <c r="F80" s="13"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="11"/>
     </row>
     <row r="81" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="1" t="s">
@@ -2000,30 +2206,30 @@
       <c r="B81" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E81" s="5"/>
-      <c r="F81" s="13"/>
+      <c r="F81" s="11"/>
     </row>
     <row r="82" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D82" s="8" t="s">
+      <c r="D82" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E82" s="8"/>
-      <c r="F82" s="13"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="11"/>
     </row>
     <row r="83" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="1" t="s">
@@ -2039,23 +2245,23 @@
         <v>16</v>
       </c>
       <c r="E83" s="5"/>
-      <c r="F83" s="13"/>
+      <c r="F83" s="11"/>
     </row>
     <row r="84" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C84" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D84" s="8" t="s">
+      <c r="C84" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E84" s="8"/>
-      <c r="F84" s="13"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="11"/>
     </row>
     <row r="85" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="1" t="s">
@@ -2071,7 +2277,7 @@
         <v>16</v>
       </c>
       <c r="E85" s="5"/>
-      <c r="F85" s="13"/>
+      <c r="F85" s="11"/>
     </row>
     <row r="86" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="1" t="s">
@@ -2087,23 +2293,23 @@
         <v>35</v>
       </c>
       <c r="E86" s="5"/>
-      <c r="F86" s="13"/>
+      <c r="F86" s="11"/>
     </row>
     <row r="87" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B87" s="7" t="s">
+      <c r="B87" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C87" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D87" s="8" t="s">
+      <c r="C87" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D87" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E87" s="8"/>
-      <c r="F87" s="13"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="11"/>
     </row>
     <row r="88" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="1" t="s">
@@ -2119,55 +2325,55 @@
         <v>35</v>
       </c>
       <c r="E88" s="5"/>
-      <c r="F88" s="13"/>
+      <c r="F88" s="11"/>
     </row>
     <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D89" s="8" t="s">
+      <c r="D89" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E89" s="8"/>
-      <c r="F89" s="13"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="11"/>
     </row>
     <row r="90" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E90" s="5"/>
-      <c r="F90" s="13"/>
+      <c r="F90" s="11"/>
     </row>
     <row r="91" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D91" s="8" t="s">
+      <c r="D91" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E91" s="8"/>
-      <c r="F91" s="13"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="11"/>
     </row>
     <row r="92" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="1" t="s">
@@ -2183,23 +2389,23 @@
         <v>12</v>
       </c>
       <c r="E92" s="5"/>
-      <c r="F92" s="13"/>
+      <c r="F92" s="11"/>
     </row>
     <row r="93" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="B93" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C93" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D93" s="8" t="s">
+      <c r="C93" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E93" s="8"/>
-      <c r="F93" s="13"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="11"/>
     </row>
     <row r="94" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="1" t="s">
@@ -2215,7 +2421,7 @@
         <v>12</v>
       </c>
       <c r="E94" s="5"/>
-      <c r="F94" s="13"/>
+      <c r="F94" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
